--- a/artfynd/A 18268-2024 artfynd.xlsx
+++ b/artfynd/A 18268-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117585657</v>
+        <v>117585306</v>
       </c>
       <c r="B2" t="n">
-        <v>56499</v>
+        <v>89901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>5685</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fula kärret (Svängbågen), Ög</t>
+          <t>Kramgölsbottnen (Kramgölsbottnen), Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573866</v>
+        <v>573925</v>
       </c>
       <c r="R2" t="n">
-        <v>6516120</v>
+        <v>6516135</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117585390</v>
+        <v>117585657</v>
       </c>
       <c r="B3" t="n">
-        <v>97753</v>
+        <v>56499</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kramgölsbottnen (Kramgölsbottnen), Ög</t>
+          <t>Fula kärret (Svängbågen), Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573925</v>
+        <v>573866</v>
       </c>
       <c r="R3" t="n">
-        <v>6516135</v>
+        <v>6516120</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117585306</v>
+        <v>117585390</v>
       </c>
       <c r="B4" t="n">
-        <v>89901</v>
+        <v>97753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 18268-2024 artfynd.xlsx
+++ b/artfynd/A 18268-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117585306</v>
       </c>
       <c r="B2" t="n">
-        <v>89901</v>
+        <v>89903</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>117585657</v>
       </c>
       <c r="B3" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>117585390</v>
       </c>
       <c r="B4" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>117588935</v>
       </c>
       <c r="B5" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18268-2024 artfynd.xlsx
+++ b/artfynd/A 18268-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117585657</v>
+        <v>117585390</v>
       </c>
       <c r="B3" t="n">
-        <v>56500</v>
+        <v>97755</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fula kärret (Svängbågen), Ög</t>
+          <t>Kramgölsbottnen (Kramgölsbottnen), Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573866</v>
+        <v>573925</v>
       </c>
       <c r="R3" t="n">
-        <v>6516120</v>
+        <v>6516135</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117585390</v>
+        <v>117585657</v>
       </c>
       <c r="B4" t="n">
-        <v>97755</v>
+        <v>56500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kramgölsbottnen (Kramgölsbottnen), Ög</t>
+          <t>Fula kärret (Svängbågen), Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573925</v>
+        <v>573866</v>
       </c>
       <c r="R4" t="n">
-        <v>6516135</v>
+        <v>6516120</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
